--- a/对照表.xlsx
+++ b/对照表.xlsx
@@ -1119,17 +1119,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B38" s="3" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>核全</t>
+        </is>
+      </c>
       <c r="C38" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1137,17 +1137,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B39" s="3" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>核有</t>
+        </is>
+      </c>
       <c r="C39" t="inlineStr">
         <is>
           <t>any</t>
         </is>
       </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1173,17 +1173,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B41" s="3" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>核二进</t>
+        </is>
+      </c>
       <c r="C41" t="inlineStr">
         <is>
           <t>bin</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1191,17 +1191,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B42" s="3" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>核布尔</t>
+        </is>
+      </c>
       <c r="C42" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1245,17 +1245,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>核可调</t>
+        </is>
+      </c>
       <c r="C45" t="inlineStr">
         <is>
           <t>callable</t>
         </is>
       </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1263,17 +1263,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B46" s="3" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>核字符号</t>
+        </is>
+      </c>
       <c r="C46" t="inlineStr">
         <is>
           <t>chr</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1317,17 +1317,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B49" s="3" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>核复数</t>
+        </is>
+      </c>
       <c r="C49" t="inlineStr">
         <is>
           <t>complex</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1335,17 +1335,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B50" s="3" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>核删属</t>
+        </is>
+      </c>
       <c r="C50" t="inlineStr">
         <is>
           <t>delattr</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1371,17 +1371,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B52" s="3" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>核目录</t>
+        </is>
+      </c>
       <c r="C52" t="inlineStr">
         <is>
           <t>dir</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1389,17 +1389,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B53" s="3" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>核除余</t>
+        </is>
+      </c>
       <c r="C53" t="inlineStr">
         <is>
           <t>divmod</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1407,17 +1407,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B54" s="3" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>核编号</t>
+        </is>
+      </c>
       <c r="C54" t="inlineStr">
         <is>
           <t>enumerate</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1425,17 +1425,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B55" s="3" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>核求值</t>
+        </is>
+      </c>
       <c r="C55" t="inlineStr">
         <is>
           <t>eval</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1443,17 +1443,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B56" s="3" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>核执行</t>
+        </is>
+      </c>
       <c r="C56" t="inlineStr">
         <is>
           <t>exec</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1461,17 +1461,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B57" s="3" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>核筛选</t>
+        </is>
+      </c>
       <c r="C57" t="inlineStr">
         <is>
           <t>filter</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1497,17 +1497,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B59" s="3" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>核格化</t>
+        </is>
+      </c>
       <c r="C59" t="inlineStr">
         <is>
           <t>format</t>
         </is>
       </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1515,17 +1515,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>核冻结集</t>
+        </is>
+      </c>
       <c r="C60" t="inlineStr">
         <is>
           <t>frozenset</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1533,17 +1533,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B61" s="3" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>核取属</t>
+        </is>
+      </c>
       <c r="C61" t="inlineStr">
         <is>
           <t>getattr</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1551,17 +1551,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B62" s="3" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>核全局表</t>
+        </is>
+      </c>
       <c r="C62" t="inlineStr">
         <is>
           <t>globals</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1569,17 +1569,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B63" s="3" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>核有属</t>
+        </is>
+      </c>
       <c r="C63" t="inlineStr">
         <is>
           <t>hasattr</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1587,17 +1587,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B64" s="3" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>核哈希</t>
+        </is>
+      </c>
       <c r="C64" t="inlineStr">
         <is>
           <t>hash</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1605,17 +1605,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B65" s="3" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>核帮助</t>
+        </is>
+      </c>
       <c r="C65" t="inlineStr">
         <is>
           <t>help</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1623,17 +1623,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B66" s="3" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>核十六</t>
+        </is>
+      </c>
       <c r="C66" t="inlineStr">
         <is>
           <t>hex</t>
         </is>
       </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1641,17 +1641,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B67" s="3" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>核编号值</t>
+        </is>
+      </c>
       <c r="C67" t="inlineStr">
         <is>
           <t>id</t>
         </is>
       </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1695,17 +1695,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B70" s="3" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>核是类</t>
+        </is>
+      </c>
       <c r="C70" t="inlineStr">
         <is>
           <t>isinstance</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1713,17 +1713,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B71" s="3" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>核是子类</t>
+        </is>
+      </c>
       <c r="C71" t="inlineStr">
         <is>
           <t>issubclass</t>
         </is>
       </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1731,17 +1731,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B72" s="3" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>核迭代</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
           <t>iter</t>
         </is>
       </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1785,17 +1785,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>核局部表</t>
+        </is>
+      </c>
       <c r="C75" t="inlineStr">
         <is>
           <t>locals</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1803,17 +1803,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B76" s="3" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>核映射</t>
+        </is>
+      </c>
       <c r="C76" t="inlineStr">
         <is>
           <t>map</t>
         </is>
       </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1875,17 +1875,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B80" s="3" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>核下一个</t>
+        </is>
+      </c>
       <c r="C80" t="inlineStr">
         <is>
           <t>next</t>
         </is>
       </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1893,17 +1893,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B81" s="3" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>核对象</t>
+        </is>
+      </c>
       <c r="C81" t="inlineStr">
         <is>
           <t>object</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1911,17 +1911,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B82" s="3" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>核八进</t>
+        </is>
+      </c>
       <c r="C82" t="inlineStr">
         <is>
           <t>oct</t>
         </is>
       </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1929,17 +1929,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B83" s="3" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>核打开</t>
+        </is>
+      </c>
       <c r="C83" t="inlineStr">
         <is>
           <t>open</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1947,17 +1947,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B84" s="3" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>核码位</t>
+        </is>
+      </c>
       <c r="C84" t="inlineStr">
         <is>
           <t>ord</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1965,17 +1965,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B85" s="3" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>核乘方</t>
+        </is>
+      </c>
       <c r="C85" t="inlineStr">
         <is>
           <t>pow</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2037,17 +2037,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B89" s="3" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>核表示</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
           <t>repr</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2055,17 +2055,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B90" s="3" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>核反排</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
           <t>reversed</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2109,17 +2109,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B93" s="3" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>核设属</t>
+        </is>
+      </c>
       <c r="C93" t="inlineStr">
         <is>
           <t>setattr</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2127,17 +2127,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B94" s="3" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>核切片</t>
+        </is>
+      </c>
       <c r="C94" t="inlineStr">
         <is>
           <t>slice</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2199,17 +2199,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B98" s="3" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>核求和</t>
+        </is>
+      </c>
       <c r="C98" t="inlineStr">
         <is>
           <t>sum</t>
         </is>
       </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -2217,17 +2217,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B99" s="3" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>核父类</t>
+        </is>
+      </c>
       <c r="C99" t="inlineStr">
         <is>
           <t>super</t>
         </is>
       </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -2235,17 +2235,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>核元组</t>
+        </is>
+      </c>
       <c r="C100" t="inlineStr">
         <is>
           <t>tuple</t>
         </is>
       </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -2253,17 +2253,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B101" s="3" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>核类型</t>
+        </is>
+      </c>
       <c r="C101" t="inlineStr">
         <is>
           <t>type</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -2271,17 +2271,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B102" s="3" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>核变量表</t>
+        </is>
+      </c>
       <c r="C102" t="inlineStr">
         <is>
           <t>vars</t>
         </is>
       </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -2289,17 +2289,17 @@
           <t>二、内置函数</t>
         </is>
       </c>
-      <c r="B103" s="3" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>核拉链</t>
+        </is>
+      </c>
       <c r="C103" t="inlineStr">
         <is>
           <t>zip</t>
         </is>
       </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -2325,17 +2325,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>核清空</t>
+        </is>
+      </c>
       <c r="C105" t="inlineStr">
         <is>
           <t>clear</t>
         </is>
       </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -2397,17 +2397,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B109" s="3" t="inlineStr"/>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>核位序</t>
+        </is>
+      </c>
       <c r="C109" t="inlineStr">
         <is>
           <t>index</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -2451,17 +2451,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B112" s="3" t="inlineStr"/>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>核移除</t>
+        </is>
+      </c>
       <c r="C112" t="inlineStr">
         <is>
           <t>remove</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -2505,17 +2505,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B115" s="3" t="inlineStr"/>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>核首大写</t>
+        </is>
+      </c>
       <c r="C115" t="inlineStr">
         <is>
           <t>capitalize</t>
         </is>
       </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -2541,17 +2541,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B117" s="3" t="inlineStr"/>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>核居中</t>
+        </is>
+      </c>
       <c r="C117" t="inlineStr">
         <is>
           <t>center</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -2577,17 +2577,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B119" s="3" t="inlineStr"/>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>核展制表</t>
+        </is>
+      </c>
       <c r="C119" t="inlineStr">
         <is>
           <t>expandtabs</t>
         </is>
       </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -2631,17 +2631,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B122" s="3" t="inlineStr"/>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>核是字数值</t>
+        </is>
+      </c>
       <c r="C122" t="inlineStr">
         <is>
           <t>isalnum</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2649,17 +2649,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B123" s="3" t="inlineStr"/>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>核是字母</t>
+        </is>
+      </c>
       <c r="C123" t="inlineStr">
         <is>
           <t>isalpha</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2685,17 +2685,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B125" s="3" t="inlineStr"/>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>核是十进制串</t>
+        </is>
+      </c>
       <c r="C125" t="inlineStr">
         <is>
           <t>isdecimal</t>
         </is>
       </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2703,17 +2703,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B126" s="3" t="inlineStr"/>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>核是数字</t>
+        </is>
+      </c>
       <c r="C126" t="inlineStr">
         <is>
           <t>isdigit</t>
         </is>
       </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2721,17 +2721,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B127" s="3" t="inlineStr"/>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>核是标识符</t>
+        </is>
+      </c>
       <c r="C127" t="inlineStr">
         <is>
           <t>isidentifier</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2739,17 +2739,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B128" s="3" t="inlineStr"/>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>核是小写</t>
+        </is>
+      </c>
       <c r="C128" t="inlineStr">
         <is>
           <t>islower</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2757,17 +2757,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr"/>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>核是数值</t>
+        </is>
+      </c>
       <c r="C129" t="inlineStr">
         <is>
           <t>isnumeric</t>
         </is>
       </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2775,17 +2775,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B130" s="3" t="inlineStr"/>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>核可打印</t>
+        </is>
+      </c>
       <c r="C130" t="inlineStr">
         <is>
           <t>isprintable</t>
         </is>
       </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2793,17 +2793,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B131" s="3" t="inlineStr"/>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>核是空白</t>
+        </is>
+      </c>
       <c r="C131" t="inlineStr">
         <is>
           <t>isspace</t>
         </is>
       </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2811,17 +2811,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B132" s="3" t="inlineStr"/>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>核是标题式</t>
+        </is>
+      </c>
       <c r="C132" t="inlineStr">
         <is>
           <t>istitle</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2829,17 +2829,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B133" s="3" t="inlineStr"/>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>核是大写</t>
+        </is>
+      </c>
       <c r="C133" t="inlineStr">
         <is>
           <t>isupper</t>
         </is>
       </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2865,17 +2865,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B135" s="3" t="inlineStr"/>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>核左齐</t>
+        </is>
+      </c>
       <c r="C135" t="inlineStr">
         <is>
           <t>ljust</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2919,17 +2919,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B138" s="3" t="inlineStr"/>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>核三分</t>
+        </is>
+      </c>
       <c r="C138" t="inlineStr">
         <is>
           <t>partition</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2955,17 +2955,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B140" s="3" t="inlineStr"/>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>核右找</t>
+        </is>
+      </c>
       <c r="C140" t="inlineStr">
         <is>
           <t>rfind</t>
         </is>
       </c>
-      <c r="D140" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2973,17 +2973,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B141" s="3" t="inlineStr"/>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>核右位序</t>
+        </is>
+      </c>
       <c r="C141" t="inlineStr">
         <is>
           <t>rindex</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2991,17 +2991,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B142" s="3" t="inlineStr"/>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>核右齐</t>
+        </is>
+      </c>
       <c r="C142" t="inlineStr">
         <is>
           <t>rjust</t>
         </is>
       </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -3009,17 +3009,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B143" s="3" t="inlineStr"/>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>核右三分</t>
+        </is>
+      </c>
       <c r="C143" t="inlineStr">
         <is>
           <t>rpartition</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -3027,17 +3027,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B144" s="3" t="inlineStr"/>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>核右木亥</t>
+        </is>
+      </c>
       <c r="C144" t="inlineStr">
         <is>
           <t>rsplit</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -3135,17 +3135,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B150" s="3" t="inlineStr"/>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>核换大小</t>
+        </is>
+      </c>
       <c r="C150" t="inlineStr">
         <is>
           <t>swapcase</t>
         </is>
       </c>
-      <c r="D150" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -3153,17 +3153,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B151" s="3" t="inlineStr"/>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>核标题式</t>
+        </is>
+      </c>
       <c r="C151" t="inlineStr">
         <is>
           <t>title</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -3171,17 +3171,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B152" s="3" t="inlineStr"/>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>核翻译</t>
+        </is>
+      </c>
       <c r="C152" t="inlineStr">
         <is>
           <t>translate</t>
         </is>
       </c>
-      <c r="D152" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -3207,17 +3207,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B154" s="3" t="inlineStr"/>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>核补零</t>
+        </is>
+      </c>
       <c r="C154" t="inlineStr">
         <is>
           <t>zfill</t>
         </is>
       </c>
-      <c r="D154" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -3225,17 +3225,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B155" s="3" t="inlineStr"/>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>核添加</t>
+        </is>
+      </c>
       <c r="C155" t="inlineStr">
         <is>
           <t>add</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -3243,17 +3243,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B156" s="3" t="inlineStr"/>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>核差集</t>
+        </is>
+      </c>
       <c r="C156" t="inlineStr">
         <is>
           <t>difference</t>
         </is>
       </c>
-      <c r="D156" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -3261,17 +3261,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B157" s="3" t="inlineStr"/>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>核差集更新</t>
+        </is>
+      </c>
       <c r="C157" t="inlineStr">
         <is>
           <t>difference_update</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -3279,17 +3279,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B158" s="3" t="inlineStr"/>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>核舍弃</t>
+        </is>
+      </c>
       <c r="C158" t="inlineStr">
         <is>
           <t>discard</t>
         </is>
       </c>
-      <c r="D158" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -3297,17 +3297,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B159" s="3" t="inlineStr"/>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>核交集</t>
+        </is>
+      </c>
       <c r="C159" t="inlineStr">
         <is>
           <t>intersection</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -3315,17 +3315,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B160" s="3" t="inlineStr"/>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>核交集更新</t>
+        </is>
+      </c>
       <c r="C160" t="inlineStr">
         <is>
           <t>intersection_update</t>
         </is>
       </c>
-      <c r="D160" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -3333,17 +3333,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B161" s="3" t="inlineStr"/>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>核不相交</t>
+        </is>
+      </c>
       <c r="C161" t="inlineStr">
         <is>
           <t>isdisjoint</t>
         </is>
       </c>
-      <c r="D161" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -3351,17 +3351,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B162" s="3" t="inlineStr"/>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>核是子集</t>
+        </is>
+      </c>
       <c r="C162" t="inlineStr">
         <is>
           <t>issubset</t>
         </is>
       </c>
-      <c r="D162" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -3369,17 +3369,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr"/>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>核是超集</t>
+        </is>
+      </c>
       <c r="C163" t="inlineStr">
         <is>
           <t>issuperset</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -3387,17 +3387,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B164" s="3" t="inlineStr"/>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>核对称差</t>
+        </is>
+      </c>
       <c r="C164" t="inlineStr">
         <is>
           <t>symmetric_difference</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -3405,17 +3405,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B165" s="3" t="inlineStr"/>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>核对称差更新</t>
+        </is>
+      </c>
       <c r="C165" t="inlineStr">
         <is>
           <t>symmetric_difference_update</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -3423,17 +3423,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B166" s="3" t="inlineStr"/>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>核并集</t>
+        </is>
+      </c>
       <c r="C166" t="inlineStr">
         <is>
           <t>union</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -3531,17 +3531,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B172" s="3" t="inlineStr"/>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>核取默认</t>
+        </is>
+      </c>
       <c r="C172" t="inlineStr">
         <is>
           <t>setdefault</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -3549,17 +3549,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B173" s="3" t="inlineStr"/>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>核弹项</t>
+        </is>
+      </c>
       <c r="C173" t="inlineStr">
         <is>
           <t>popitem</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -3567,17 +3567,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B174" s="3" t="inlineStr"/>
+      <c r="B174" s="2" t="inlineStr">
+        <is>
+          <t>核建字典</t>
+        </is>
+      </c>
       <c r="C174" t="inlineStr">
         <is>
           <t>fromkeys</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -3585,17 +3585,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B175" s="3" t="inlineStr"/>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>核读取</t>
+        </is>
+      </c>
       <c r="C175" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -3603,17 +3603,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B176" s="3" t="inlineStr"/>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>核读行</t>
+        </is>
+      </c>
       <c r="C176" t="inlineStr">
         <is>
           <t>readline</t>
         </is>
       </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -3621,17 +3621,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr"/>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>核读多行</t>
+        </is>
+      </c>
       <c r="C177" t="inlineStr">
         <is>
           <t>readlines</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -3639,17 +3639,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B178" s="3" t="inlineStr"/>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>核写入</t>
+        </is>
+      </c>
       <c r="C178" t="inlineStr">
         <is>
           <t>write</t>
         </is>
       </c>
-      <c r="D178" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -3657,17 +3657,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B179" s="3" t="inlineStr"/>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>核写多行</t>
+        </is>
+      </c>
       <c r="C179" t="inlineStr">
         <is>
           <t>writelines</t>
         </is>
       </c>
-      <c r="D179" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -3675,17 +3675,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B180" s="3" t="inlineStr"/>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
+          <t>核关闭</t>
+        </is>
+      </c>
       <c r="C180" t="inlineStr">
         <is>
           <t>close</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -3693,17 +3693,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B181" s="3" t="inlineStr"/>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>核定位</t>
+        </is>
+      </c>
       <c r="C181" t="inlineStr">
         <is>
           <t>seek</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -3711,17 +3711,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B182" s="3" t="inlineStr"/>
+      <c r="B182" s="2" t="inlineStr">
+        <is>
+          <t>核位置</t>
+        </is>
+      </c>
       <c r="C182" t="inlineStr">
         <is>
           <t>tell</t>
         </is>
       </c>
-      <c r="D182" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -3729,17 +3729,17 @@
           <t>三、方法</t>
         </is>
       </c>
-      <c r="B183" s="3" t="inlineStr"/>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>核即刷</t>
+        </is>
+      </c>
       <c r="C183" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="D183" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -3783,17 +3783,17 @@
           <t>四、关键字参数</t>
         </is>
       </c>
-      <c r="B186" s="3" t="inlineStr"/>
+      <c r="B186" s="2" t="inlineStr">
+        <is>
+          <t>核文件</t>
+        </is>
+      </c>
       <c r="C186" t="inlineStr">
         <is>
           <t>file</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -3801,17 +3801,17 @@
           <t>四、关键字参数</t>
         </is>
       </c>
-      <c r="B187" s="3" t="inlineStr"/>
+      <c r="B187" s="2" t="inlineStr">
+        <is>
+          <t>核刷新</t>
+        </is>
+      </c>
       <c r="C187" t="inlineStr">
         <is>
           <t>flush</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -3819,17 +3819,17 @@
           <t>四、关键字参数</t>
         </is>
       </c>
-      <c r="B188" s="3" t="inlineStr"/>
+      <c r="B188" s="2" t="inlineStr">
+        <is>
+          <t>核键序</t>
+        </is>
+      </c>
       <c r="C188" t="inlineStr">
         <is>
           <t>key</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -3837,17 +3837,17 @@
           <t>四、关键字参数</t>
         </is>
       </c>
-      <c r="B189" s="3" t="inlineStr"/>
+      <c r="B189" s="2" t="inlineStr">
+        <is>
+          <t>核反序</t>
+        </is>
+      </c>
       <c r="C189" t="inlineStr">
         <is>
           <t>reverse</t>
         </is>
       </c>
-      <c r="D189" t="inlineStr">
-        <is>
-          <t>待定义</t>
-        </is>
-      </c>
+      <c r="D189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">

--- a/对照表.xlsx
+++ b/对照表.xlsx
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>核目录</t>
+          <t>核列属</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
